--- a/stencil/2、基层单位采购价差表（电子版）.xlsx
+++ b/stencil/2、基层单位采购价差表（电子版）.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14175"/>
+    <workbookView windowWidth="17670" windowHeight="7245"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
